--- a/App_Control_Servo_Press_Delta/bin/Debug/Template/Template_History.xlsx
+++ b/App_Control_Servo_Press_Delta/bin/Debug/Template/Template_History.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cong Viec\STI\Du An\12.Control_Servo_Press_Delta\12.Control_Servo_Press_Delta\Control_Servo_Press_Delta\bin\Debug\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cong Viec\STI\Du An\06.Control_Servo_Press_Delta\App_Control_Servo_Press_Delta\App_Control_Servo_Press_Delta\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC63236E-75DA-4383-86F2-896EE1FB88D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C672F10-4301-4323-8DD6-FC010CC41CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2985" yWindow="2985" windowWidth="21600" windowHeight="11385" xr2:uid="{E218F110-D790-4754-92A7-CE5EF34DA3DA}"/>
+    <workbookView xWindow="-26115" yWindow="2685" windowWidth="21600" windowHeight="11385" xr2:uid="{D51AC33A-CE97-4BBA-B91C-5AE76BC5A49F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,34 +25,344 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>Code</t>
   </si>
   <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>Solution</t>
+    <t>Solution: Cách khắc phục</t>
+  </si>
+  <si>
+    <t>Description: Nội dung lỗi</t>
+  </si>
+  <si>
+    <t>Code: EXY(E: Error, A: Alarm X: Thanh ghi, Y: Bit) dựa vào thanh ghi trên PLC</t>
+  </si>
+  <si>
+    <t>Không sửa dữ liệu Code, không có Description và Solution vui lòng để trống</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>E15</t>
+  </si>
+  <si>
+    <t>E16</t>
+  </si>
+  <si>
+    <t>E17</t>
+  </si>
+  <si>
+    <t>E18</t>
+  </si>
+  <si>
+    <t>E19</t>
+  </si>
+  <si>
+    <t>E1A</t>
+  </si>
+  <si>
+    <t>E1B</t>
+  </si>
+  <si>
+    <t>E1C</t>
+  </si>
+  <si>
+    <t>E1D</t>
+  </si>
+  <si>
+    <t>E1E</t>
+  </si>
+  <si>
+    <t>E1F</t>
+  </si>
+  <si>
+    <t>E20</t>
+  </si>
+  <si>
+    <t>E21</t>
+  </si>
+  <si>
+    <t>E22</t>
+  </si>
+  <si>
+    <t>E23</t>
+  </si>
+  <si>
+    <t>E24</t>
+  </si>
+  <si>
+    <t>E25</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>E27</t>
+  </si>
+  <si>
+    <t>E28</t>
+  </si>
+  <si>
+    <t>E29</t>
+  </si>
+  <si>
+    <t>E2A</t>
+  </si>
+  <si>
+    <t>E2B</t>
+  </si>
+  <si>
+    <t>E2C</t>
+  </si>
+  <si>
+    <t>E2D</t>
+  </si>
+  <si>
+    <t>E2E</t>
+  </si>
+  <si>
+    <t>E2F</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>A16</t>
+  </si>
+  <si>
+    <t>A17</t>
+  </si>
+  <si>
+    <t>A18</t>
+  </si>
+  <si>
+    <t>A19</t>
+  </si>
+  <si>
+    <t>A1A</t>
+  </si>
+  <si>
+    <t>A1B</t>
+  </si>
+  <si>
+    <t>A1C</t>
+  </si>
+  <si>
+    <t>A1D</t>
+  </si>
+  <si>
+    <t>A1E</t>
+  </si>
+  <si>
+    <t>A1F</t>
+  </si>
+  <si>
+    <t>E30</t>
+  </si>
+  <si>
+    <t>E33</t>
+  </si>
+  <si>
+    <t>E32</t>
+  </si>
+  <si>
+    <t>E34</t>
+  </si>
+  <si>
+    <t>E35</t>
+  </si>
+  <si>
+    <t>E36</t>
+  </si>
+  <si>
+    <t>E37</t>
+  </si>
+  <si>
+    <t>E38</t>
+  </si>
+  <si>
+    <t>E39</t>
+  </si>
+  <si>
+    <t>E3A</t>
+  </si>
+  <si>
+    <t>E3B</t>
+  </si>
+  <si>
+    <t>E3C</t>
+  </si>
+  <si>
+    <t>E3D</t>
+  </si>
+  <si>
+    <t>E3E</t>
+  </si>
+  <si>
+    <t>E3F</t>
+  </si>
+  <si>
+    <t>E40</t>
+  </si>
+  <si>
+    <t>E44</t>
+  </si>
+  <si>
+    <t>E42</t>
+  </si>
+  <si>
+    <t>E45</t>
+  </si>
+  <si>
+    <t>E46</t>
+  </si>
+  <si>
+    <t>E47</t>
+  </si>
+  <si>
+    <t>E48</t>
+  </si>
+  <si>
+    <t>E49</t>
+  </si>
+  <si>
+    <t>E4A</t>
+  </si>
+  <si>
+    <t>E4B</t>
+  </si>
+  <si>
+    <t>E4C</t>
+  </si>
+  <si>
+    <t>E4D</t>
+  </si>
+  <si>
+    <t>E4E</t>
+  </si>
+  <si>
+    <t>E4F</t>
+  </si>
+  <si>
+    <t>E41</t>
+  </si>
+  <si>
+    <t>E50</t>
+  </si>
+  <si>
+    <t>E51</t>
+  </si>
+  <si>
+    <t>E52</t>
+  </si>
+  <si>
+    <t>E53</t>
+  </si>
+  <si>
+    <t>E54</t>
+  </si>
+  <si>
+    <t>E55</t>
+  </si>
+  <si>
+    <t>E56</t>
+  </si>
+  <si>
+    <t>E57</t>
+  </si>
+  <si>
+    <t>E58</t>
+  </si>
+  <si>
+    <t>E59</t>
+  </si>
+  <si>
+    <t>E5A</t>
+  </si>
+  <si>
+    <t>E5B</t>
+  </si>
+  <si>
+    <t>E5C</t>
+  </si>
+  <si>
+    <t>E5D</t>
+  </si>
+  <si>
+    <t>E5E</t>
+  </si>
+  <si>
+    <t>E5F</t>
+  </si>
+  <si>
+    <t>Description_EN</t>
+  </si>
+  <si>
+    <t>Solution_EN</t>
+  </si>
+  <si>
+    <t>Description_VN</t>
+  </si>
+  <si>
+    <t>Solution_VN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -63,7 +373,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,15 +381,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,22 +720,921 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF27A90-AD33-43DB-82F0-C14E352E8ED6}">
-  <dimension ref="A1:C1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7DC92C-1EAE-4F87-BA71-750C80FEC939}">
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="49" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/App_Control_Servo_Press_Delta/bin/Debug/Template/Template_History.xlsx
+++ b/App_Control_Servo_Press_Delta/bin/Debug/Template/Template_History.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cong Viec\STI\Du An\06.Control_Servo_Press_Delta\App_Control_Servo_Press_Delta\App_Control_Servo_Press_Delta\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C672F10-4301-4323-8DD6-FC010CC41CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01C3304-488F-4278-83D8-2D2AE99A484F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26115" yWindow="2685" windowWidth="21600" windowHeight="11385" xr2:uid="{D51AC33A-CE97-4BBA-B91C-5AE76BC5A49F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D51AC33A-CE97-4BBA-B91C-5AE76BC5A49F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>Code</t>
   </si>
@@ -231,99 +231,6 @@
     <t>E3F</t>
   </si>
   <si>
-    <t>E40</t>
-  </si>
-  <si>
-    <t>E44</t>
-  </si>
-  <si>
-    <t>E42</t>
-  </si>
-  <si>
-    <t>E45</t>
-  </si>
-  <si>
-    <t>E46</t>
-  </si>
-  <si>
-    <t>E47</t>
-  </si>
-  <si>
-    <t>E48</t>
-  </si>
-  <si>
-    <t>E49</t>
-  </si>
-  <si>
-    <t>E4A</t>
-  </si>
-  <si>
-    <t>E4B</t>
-  </si>
-  <si>
-    <t>E4C</t>
-  </si>
-  <si>
-    <t>E4D</t>
-  </si>
-  <si>
-    <t>E4E</t>
-  </si>
-  <si>
-    <t>E4F</t>
-  </si>
-  <si>
-    <t>E41</t>
-  </si>
-  <si>
-    <t>E50</t>
-  </si>
-  <si>
-    <t>E51</t>
-  </si>
-  <si>
-    <t>E52</t>
-  </si>
-  <si>
-    <t>E53</t>
-  </si>
-  <si>
-    <t>E54</t>
-  </si>
-  <si>
-    <t>E55</t>
-  </si>
-  <si>
-    <t>E56</t>
-  </si>
-  <si>
-    <t>E57</t>
-  </si>
-  <si>
-    <t>E58</t>
-  </si>
-  <si>
-    <t>E59</t>
-  </si>
-  <si>
-    <t>E5A</t>
-  </si>
-  <si>
-    <t>E5B</t>
-  </si>
-  <si>
-    <t>E5C</t>
-  </si>
-  <si>
-    <t>E5D</t>
-  </si>
-  <si>
-    <t>E5E</t>
-  </si>
-  <si>
-    <t>E5F</t>
-  </si>
-  <si>
     <t>Description_EN</t>
   </si>
   <si>
@@ -334,6 +241,102 @@
   </si>
   <si>
     <t>Solution_VN</t>
+  </si>
+  <si>
+    <t>E00</t>
+  </si>
+  <si>
+    <t>E01</t>
+  </si>
+  <si>
+    <t>E02</t>
+  </si>
+  <si>
+    <t>E03</t>
+  </si>
+  <si>
+    <t>E04</t>
+  </si>
+  <si>
+    <t>E05</t>
+  </si>
+  <si>
+    <t>E06</t>
+  </si>
+  <si>
+    <t>E07</t>
+  </si>
+  <si>
+    <t>E08</t>
+  </si>
+  <si>
+    <t>E09</t>
+  </si>
+  <si>
+    <t>E0A</t>
+  </si>
+  <si>
+    <t>E0B</t>
+  </si>
+  <si>
+    <t>E0C</t>
+  </si>
+  <si>
+    <t>E0D</t>
+  </si>
+  <si>
+    <t>E0E</t>
+  </si>
+  <si>
+    <t>E0F</t>
+  </si>
+  <si>
+    <t>A00</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>A0A</t>
+  </si>
+  <si>
+    <t>A0B</t>
+  </si>
+  <si>
+    <t>A0C</t>
+  </si>
+  <si>
+    <t>A0D</t>
+  </si>
+  <si>
+    <t>A0E</t>
+  </si>
+  <si>
+    <t>A0F</t>
   </si>
 </sst>
 </file>
@@ -756,21 +759,21 @@
         <v>0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -779,7 +782,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -788,7 +791,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -797,7 +800,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -806,7 +809,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -815,7 +818,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -824,7 +827,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -833,7 +836,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -842,7 +845,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -851,7 +854,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -860,7 +863,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -869,7 +872,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -878,7 +881,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -887,7 +890,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -896,7 +899,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -905,7 +908,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -914,7 +917,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -923,7 +926,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -932,7 +935,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -941,7 +944,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -950,7 +953,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -959,7 +962,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -968,7 +971,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -977,7 +980,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -986,7 +989,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -995,7 +998,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1004,7 +1007,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1013,7 +1016,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1022,7 +1025,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1031,7 +1034,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1040,7 +1043,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1049,7 +1052,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1058,7 +1061,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1067,7 +1070,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1076,7 +1079,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1085,7 +1088,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1094,7 +1097,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1103,7 +1106,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1112,7 +1115,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1121,7 +1124,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1130,7 +1133,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1139,7 +1142,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1148,7 +1151,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1157,7 +1160,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1166,7 +1169,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1175,7 +1178,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1184,7 +1187,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1193,7 +1196,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1202,7 +1205,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1211,7 +1214,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1220,7 +1223,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1229,7 +1232,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1238,7 +1241,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -1247,7 +1250,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -1256,7 +1259,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -1265,7 +1268,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -1274,7 +1277,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -1283,7 +1286,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -1292,7 +1295,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -1301,7 +1304,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -1310,7 +1313,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -1319,7 +1322,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -1328,7 +1331,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -1337,7 +1340,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -1346,7 +1349,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -1355,7 +1358,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -1364,7 +1367,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -1373,7 +1376,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -1382,7 +1385,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -1391,7 +1394,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -1400,7 +1403,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -1409,7 +1412,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -1418,7 +1421,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -1427,7 +1430,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -1436,7 +1439,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -1445,7 +1448,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -1454,7 +1457,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -1463,7 +1466,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -1472,7 +1475,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -1481,7 +1484,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -1490,7 +1493,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -1499,7 +1502,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -1508,7 +1511,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -1517,7 +1520,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -1526,7 +1529,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -1535,7 +1538,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -1544,7 +1547,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -1553,7 +1556,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -1562,7 +1565,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -1571,7 +1574,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -1580,7 +1583,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -1589,7 +1592,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -1598,7 +1601,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -1607,7 +1610,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -1616,7 +1619,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -1625,7 +1628,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
